--- a/LUGAR_CLAUDE.xlsx
+++ b/LUGAR_CLAUDE.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="247">
   <si>
     <t>id_lugar</t>
   </si>
@@ -285,6 +285,12 @@
   </si>
   <si>
     <t>Cabo de Vírgenes</t>
+  </si>
+  <si>
+    <t>LUG043</t>
+  </si>
+  <si>
+    <t>Palermo</t>
   </si>
   <si>
     <t>id_infraestructura</t>
@@ -1615,7 +1621,14 @@
         <v>-68.3444</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1"/>
     <row r="47" ht="15.75" customHeight="1"/>
@@ -2594,19 +2607,19 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -2617,19 +2630,19 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F2" s="11">
         <v>36.495516</v>
@@ -2640,47 +2653,47 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
@@ -2688,13 +2701,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
@@ -2702,13 +2715,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
@@ -2722,13 +2735,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>44</v>
@@ -2736,13 +2749,13 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>42</v>
@@ -2750,104 +2763,104 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F15" s="11">
         <v>23.12653</v>
@@ -2858,36 +2871,36 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F17" s="11">
         <v>36.4942</v>
@@ -2898,36 +2911,36 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -3933,337 +3946,337 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>194</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B27" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4288,74 +4301,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -4378,18 +4391,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -4414,16 +4427,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -4435,16 +4448,16 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E2" s="4">
         <v>36.818056</v>
@@ -4455,13 +4468,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E3" s="7">
         <v>35.9257</v>
@@ -4472,13 +4485,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E4" s="7">
         <v>36.25</v>

--- a/LUGAR_CLAUDE.xlsx
+++ b/LUGAR_CLAUDE.xlsx
@@ -8,20 +8,21 @@
     <sheet state="visible" name="Mercancias" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="Mercancias_caudales" sheetId="4" r:id="rId7"/>
     <sheet state="visible" name="Enfermedades" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="BATALLA" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="Causa Defunción" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="BATALLA" sheetId="7" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="P5kwSxIi6O+wpExk09GRNB0+MJP21w4XZuwvx1oovRA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="uUOBNpxdupLWAYGmnxybHA7Sjsg0LHwA/lLPOoUuAe4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="288">
   <si>
     <t>id_lugar</t>
   </si>
@@ -293,6 +294,30 @@
     <t>Palermo</t>
   </si>
   <si>
+    <t>LUG044</t>
+  </si>
+  <si>
+    <t>Talcahuano</t>
+  </si>
+  <si>
+    <t>LUG045</t>
+  </si>
+  <si>
+    <t>Peniche</t>
+  </si>
+  <si>
+    <t>LUG046</t>
+  </si>
+  <si>
+    <t>Océano Pacífico</t>
+  </si>
+  <si>
+    <t>LUG047</t>
+  </si>
+  <si>
+    <t>Bellavista</t>
+  </si>
+  <si>
     <t>id_infraestructura</t>
   </si>
   <si>
@@ -434,6 +459,24 @@
     <t>Caño de Trocadero</t>
   </si>
   <si>
+    <t>INF020</t>
+  </si>
+  <si>
+    <t>Poza de Santa Isabel</t>
+  </si>
+  <si>
+    <t>INF021</t>
+  </si>
+  <si>
+    <t>Hospital de Bellavista</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>JEF049</t>
+  </si>
+  <si>
     <t>id_mercancia</t>
   </si>
   <si>
@@ -720,6 +763,87 @@
   </si>
   <si>
     <t>Escorbuto</t>
+  </si>
+  <si>
+    <t>id_causa_defuncion</t>
+  </si>
+  <si>
+    <t>nombre_causa_defuncion</t>
+  </si>
+  <si>
+    <t>CAUDEF001</t>
+  </si>
+  <si>
+    <t>Muerto en combate</t>
+  </si>
+  <si>
+    <t>Combate</t>
+  </si>
+  <si>
+    <t>CAUDEF002</t>
+  </si>
+  <si>
+    <t>Heridas posteriores al combate</t>
+  </si>
+  <si>
+    <t>CAUDEF003</t>
+  </si>
+  <si>
+    <t>Naufragio</t>
+  </si>
+  <si>
+    <t>Accidente</t>
+  </si>
+  <si>
+    <t>CAUDEF004</t>
+  </si>
+  <si>
+    <t>Accidente a bordo</t>
+  </si>
+  <si>
+    <t>CAUDEF005</t>
+  </si>
+  <si>
+    <t>Enfermedad a bordo</t>
+  </si>
+  <si>
+    <t>Enfermedad</t>
+  </si>
+  <si>
+    <t>CAUDEF006</t>
+  </si>
+  <si>
+    <t>Enfermedad en tierra</t>
+  </si>
+  <si>
+    <t>CAUDEF007</t>
+  </si>
+  <si>
+    <t>Vejez / causas naturales</t>
+  </si>
+  <si>
+    <t>Natural</t>
+  </si>
+  <si>
+    <t>CAUDEF008</t>
+  </si>
+  <si>
+    <t>Asesinato</t>
+  </si>
+  <si>
+    <t>Violenta</t>
+  </si>
+  <si>
+    <t>CAUDEF009</t>
+  </si>
+  <si>
+    <t>Ejecución</t>
+  </si>
+  <si>
+    <t>CAUDEF010</t>
+  </si>
+  <si>
+    <t>Desconocida</t>
   </si>
   <si>
     <t>id_batalla</t>
@@ -774,7 +898,7 @@
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -817,6 +941,12 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -846,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -859,12 +989,15 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -895,6 +1028,10 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1330,6 +1467,12 @@
       <c r="B18" s="4" t="s">
         <v>37</v>
       </c>
+      <c r="C18" s="8">
+        <v>-22.881353</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-43.182717</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
@@ -1406,10 +1549,10 @@
       <c r="B26" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="9">
         <v>-27.568285</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="9">
         <v>-48.548</v>
       </c>
     </row>
@@ -1420,10 +1563,10 @@
       <c r="B27" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="9">
         <v>37.3964</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="9">
         <v>-6.4757</v>
       </c>
     </row>
@@ -1434,10 +1577,10 @@
       <c r="B28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="9">
         <v>37.3891</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="9">
         <v>-5.9845</v>
       </c>
     </row>
@@ -1448,8 +1591,8 @@
       <c r="B29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
@@ -1458,8 +1601,8 @@
       <c r="B30" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
@@ -1468,10 +1611,10 @@
       <c r="B31" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="9">
         <v>39.5681</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="9">
         <v>2.6472</v>
       </c>
     </row>
@@ -1482,8 +1625,8 @@
       <c r="B32" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
@@ -1492,10 +1635,10 @@
       <c r="B33" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="9">
         <v>-0.1807</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="9">
         <v>-78.4678</v>
       </c>
     </row>
@@ -1506,10 +1649,10 @@
       <c r="B34" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="9">
         <v>42.061</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="9">
         <v>-1.6058</v>
       </c>
     </row>
@@ -1520,10 +1663,10 @@
       <c r="B35" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="9">
         <v>42.7863</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="9">
         <v>-1.3706</v>
       </c>
     </row>
@@ -1534,10 +1677,10 @@
       <c r="B36" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="9">
         <v>41.5033</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="9">
         <v>-5.7446</v>
       </c>
     </row>
@@ -1548,10 +1691,10 @@
       <c r="B37" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="9">
         <v>36.6</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="9">
         <v>-6.233</v>
       </c>
     </row>
@@ -1570,10 +1713,10 @@
       <c r="B39" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="9">
         <v>42.4479</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="9">
         <v>-2.887</v>
       </c>
     </row>
@@ -1592,10 +1735,10 @@
       <c r="B41" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="9">
         <v>19.4325</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="9">
         <v>-99.1303</v>
       </c>
     </row>
@@ -1611,13 +1754,13 @@
       <c r="A43" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="8">
         <v>-52.33039</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="8">
         <v>-68.3444</v>
       </c>
     </row>
@@ -1625,14 +1768,60 @@
       <c r="A44" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-36.7382</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-73.1388</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="8">
+        <v>39.3764</v>
+      </c>
+      <c r="D46" s="8">
+        <v>-9.3793</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-12.0639</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-77.1314</v>
+      </c>
+    </row>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2607,19 +2796,19 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -2630,19 +2819,19 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F2" s="11">
         <v>36.495516</v>
@@ -2653,47 +2842,47 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
@@ -2701,13 +2890,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
@@ -2715,13 +2904,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
@@ -2735,13 +2924,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>44</v>
@@ -2749,13 +2938,13 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>42</v>
@@ -2763,104 +2952,104 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F15" s="11">
         <v>23.12653</v>
@@ -2871,36 +3060,36 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F17" s="11">
         <v>36.4942</v>
@@ -2911,40 +3100,78 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="8">
+        <v>-12.0639</v>
+      </c>
+      <c r="G21" s="8">
+        <v>-77.1314</v>
+      </c>
+    </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
@@ -3946,337 +4173,337 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>210</v>
+        <v>223</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -4301,74 +4528,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4390,19 +4617,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>230</v>
+      <c r="A1" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>232</v>
+      <c r="A2" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4411,6 +4638,140 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="17.5"/>
+    <col customWidth="1" min="2" max="2" width="21.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4427,16 +4788,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>235</v>
+        <v>276</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -4448,16 +4809,16 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>239</v>
+        <v>279</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>280</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="E2" s="4">
         <v>36.818056</v>
@@ -4468,13 +4829,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>243</v>
+        <v>283</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>284</v>
       </c>
       <c r="E3" s="7">
         <v>35.9257</v>
@@ -4485,13 +4846,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>246</v>
+        <v>286</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>287</v>
       </c>
       <c r="E4" s="7">
         <v>36.25</v>

--- a/LUGAR_CLAUDE.xlsx
+++ b/LUGAR_CLAUDE.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="318">
   <si>
     <t>id_lugar</t>
   </si>
@@ -318,6 +318,18 @@
     <t>Bellavista</t>
   </si>
   <si>
+    <t>LUG048</t>
+  </si>
+  <si>
+    <t>Guadalajara</t>
+  </si>
+  <si>
+    <t>LUG049</t>
+  </si>
+  <si>
+    <t>Argel</t>
+  </si>
+  <si>
     <t>id_infraestructura</t>
   </si>
   <si>
@@ -477,6 +489,18 @@
     <t>JEF049</t>
   </si>
   <si>
+    <t>INF022</t>
+  </si>
+  <si>
+    <t>Fondeadero de reparaciones</t>
+  </si>
+  <si>
+    <t>INF023</t>
+  </si>
+  <si>
+    <t>Astillero Callao</t>
+  </si>
+  <si>
     <t>id_mercancia</t>
   </si>
   <si>
@@ -588,6 +612,9 @@
     <t>Lino</t>
   </si>
   <si>
+    <t>Téxtil</t>
+  </si>
+  <si>
     <t>MER00014</t>
   </si>
   <si>
@@ -699,6 +726,51 @@
     <t>Gateado</t>
   </si>
   <si>
+    <t>MER00031</t>
+  </si>
+  <si>
+    <t>Peje tollo</t>
+  </si>
+  <si>
+    <t>MER00032</t>
+  </si>
+  <si>
+    <t>Fruteritos de piedra de Huamanga</t>
+  </si>
+  <si>
+    <t>Artesanía</t>
+  </si>
+  <si>
+    <t>MER00033</t>
+  </si>
+  <si>
+    <t>Hierbas medicinales</t>
+  </si>
+  <si>
+    <t>MER00034</t>
+  </si>
+  <si>
+    <t>Bronce</t>
+  </si>
+  <si>
+    <t>MER00035</t>
+  </si>
+  <si>
+    <t>Lana vicuña</t>
+  </si>
+  <si>
+    <t>MER00036</t>
+  </si>
+  <si>
+    <t>Calaguala</t>
+  </si>
+  <si>
+    <t>MER00037</t>
+  </si>
+  <si>
+    <t>Artesanía local</t>
+  </si>
+  <si>
     <t>id_mercancias_caudales</t>
   </si>
   <si>
@@ -751,6 +823,24 @@
   </si>
   <si>
     <t>Esmeraldas</t>
+  </si>
+  <si>
+    <t>MERCAUD00009</t>
+  </si>
+  <si>
+    <t>Oro en pasta</t>
+  </si>
+  <si>
+    <t>MERCAUD00010</t>
+  </si>
+  <si>
+    <t>Piedra de mineral de plata</t>
+  </si>
+  <si>
+    <t>MERCAUD00011</t>
+  </si>
+  <si>
+    <t>Piedras preciosas</t>
   </si>
   <si>
     <t>id_enfermedad</t>
@@ -1822,8 +1912,28 @@
         <v>-77.1314</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="8">
+        <v>36.7651</v>
+      </c>
+      <c r="D50" s="8">
+        <v>3.1676</v>
+      </c>
+    </row>
     <row r="51" ht="15.75" customHeight="1"/>
     <row r="52" ht="15.75" customHeight="1"/>
     <row r="53" ht="15.75" customHeight="1"/>
@@ -2796,19 +2906,19 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -2819,19 +2929,19 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F2" s="11">
         <v>36.495516</v>
@@ -2842,47 +2952,47 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
@@ -2890,13 +3000,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
@@ -2904,13 +3014,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
@@ -2924,13 +3034,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>44</v>
@@ -2938,13 +3048,13 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>42</v>
@@ -2952,104 +3062,104 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F15" s="11">
         <v>23.12653</v>
@@ -3060,36 +3170,36 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F17" s="11">
         <v>36.4942</v>
@@ -3100,70 +3210,70 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F21" s="8">
         <v>-12.0639</v>
@@ -3172,8 +3282,38 @@
         <v>-77.1314</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="8">
+        <v>-22.881353</v>
+      </c>
+      <c r="G22" s="8">
+        <v>-43.182717</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
@@ -4173,337 +4313,417 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>224</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4528,74 +4748,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>242</v>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -4618,18 +4862,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -4650,120 +4894,120 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4788,16 +5032,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -4809,16 +5053,16 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="E2" s="4">
         <v>36.818056</v>
@@ -4829,13 +5073,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="E3" s="7">
         <v>35.9257</v>
@@ -4846,13 +5090,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="E4" s="7">
         <v>36.25</v>

--- a/LUGAR_CLAUDE.xlsx
+++ b/LUGAR_CLAUDE.xlsx
@@ -10,19 +10,20 @@
     <sheet state="visible" name="Enfermedades" sheetId="5" r:id="rId8"/>
     <sheet state="visible" name="Causa Defunción" sheetId="6" r:id="rId9"/>
     <sheet state="visible" name="BATALLA" sheetId="7" r:id="rId10"/>
+    <sheet state="visible" name="Nacion" sheetId="8" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="uUOBNpxdupLWAYGmnxybHA7Sjsg0LHwA/lLPOoUuAe4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="x7rhIxwm+2ztIiylPbO712SLJya495PrXRWLtc2kBC8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="345">
   <si>
     <t>id_lugar</t>
   </si>
@@ -330,6 +331,30 @@
     <t>Argel</t>
   </si>
   <si>
+    <t>LUG050</t>
+  </si>
+  <si>
+    <t>Constantinopla</t>
+  </si>
+  <si>
+    <t>LUG051</t>
+  </si>
+  <si>
+    <t>Mahón</t>
+  </si>
+  <si>
+    <t>LUG052</t>
+  </si>
+  <si>
+    <t>Siracusa</t>
+  </si>
+  <si>
+    <t>LUG053</t>
+  </si>
+  <si>
+    <t>Isla Tenedós</t>
+  </si>
+  <si>
     <t>id_infraestructura</t>
   </si>
   <si>
@@ -948,6 +973,9 @@
     <t>Guerra</t>
   </si>
   <si>
+    <t>resultado</t>
+  </si>
+  <si>
     <t>BAT00001</t>
   </si>
   <si>
@@ -960,6 +988,12 @@
     <t>Guerra anglo-española (1779-1783)</t>
   </si>
   <si>
+    <t>Derrota española frente a la Royal Navy</t>
+  </si>
+  <si>
+    <t>naval</t>
+  </si>
+  <si>
     <t>BAT00002</t>
   </si>
   <si>
@@ -976,17 +1010,66 @@
   </si>
   <si>
     <t>21/10/1805</t>
+  </si>
+  <si>
+    <t>BAT00004</t>
+  </si>
+  <si>
+    <t>Combate del Castillo Nuevo</t>
+  </si>
+  <si>
+    <t>08/06/1758</t>
+  </si>
+  <si>
+    <t>victoria española</t>
+  </si>
+  <si>
+    <t>id_nacion</t>
+  </si>
+  <si>
+    <t>nombre_nacion</t>
+  </si>
+  <si>
+    <t>NACI00001</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>NACI00002</t>
+  </si>
+  <si>
+    <t>Reino Unido</t>
+  </si>
+  <si>
+    <t>NACI00003</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>NACI00004</t>
+  </si>
+  <si>
+    <t>Argelia</t>
+  </si>
+  <si>
+    <t>NACI00005</t>
+  </si>
+  <si>
+    <t>Marruecos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1066,7 +1149,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1089,6 +1172,12 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1122,6 +1211,10 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1934,10 +2027,62 @@
         <v>3.1676</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="8">
+        <v>41.0198</v>
+      </c>
+      <c r="D51" s="8">
+        <v>28.9793</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="8">
+        <v>39.8873</v>
+      </c>
+      <c r="D52" s="8">
+        <v>4.285</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="8">
+        <v>37.05996</v>
+      </c>
+      <c r="D53" s="8">
+        <v>15.2826</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="8">
+        <v>39.8125</v>
+      </c>
+      <c r="D54" s="8">
+        <v>25.9889</v>
+      </c>
+    </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1"/>
@@ -2906,19 +3051,19 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -2929,19 +3074,19 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F2" s="11">
         <v>36.495516</v>
@@ -2952,47 +3097,47 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
@@ -3000,13 +3145,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
@@ -3014,13 +3159,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
@@ -3034,13 +3179,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>44</v>
@@ -3048,13 +3193,13 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>42</v>
@@ -3062,104 +3207,104 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F15" s="11">
         <v>23.12653</v>
@@ -3170,36 +3315,36 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F17" s="11">
         <v>36.4942</v>
@@ -3210,70 +3355,70 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F21" s="8">
         <v>-12.0639</v>
@@ -3284,13 +3429,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>36</v>
@@ -3305,13 +3450,13 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
@@ -4313,417 +4458,417 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4748,98 +4893,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -4862,18 +5007,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -4894,120 +5039,120 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -5032,16 +5177,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -5049,20 +5194,25 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2"/>
+      <c r="G1" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="E2" s="4">
         <v>36.818056</v>
@@ -5070,16 +5220,22 @@
       <c r="F2" s="4">
         <v>-8.563611</v>
       </c>
+      <c r="G2" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E3" s="7">
         <v>35.9257</v>
@@ -5090,13 +5246,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="E4" s="7">
         <v>36.25</v>
@@ -5106,8 +5262,27 @@
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="A5" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="E5" s="15">
+        <v>37.1718</v>
+      </c>
+      <c r="F5" s="15">
+        <v>4.5003</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="E6" s="7"/>
@@ -5123,4 +5298,67 @@
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="16.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/LUGAR_CLAUDE.xlsx
+++ b/LUGAR_CLAUDE.xlsx
@@ -16,14 +16,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="x7rhIxwm+2ztIiylPbO712SLJya495PrXRWLtc2kBC8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="4ySy402Retz3n3BGMv3vlU6f/ndY9K+BjjgjSZUU/gk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="361">
   <si>
     <t>id_lugar</t>
   </si>
@@ -355,6 +355,36 @@
     <t>Isla Tenedós</t>
   </si>
   <si>
+    <t>LUG054</t>
+  </si>
+  <si>
+    <t>Burgos</t>
+  </si>
+  <si>
+    <t>LUG055</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>LUG056</t>
+  </si>
+  <si>
+    <t>Melilla</t>
+  </si>
+  <si>
+    <t>LUG057</t>
+  </si>
+  <si>
+    <t>Algeciras</t>
+  </si>
+  <si>
+    <t>LUG058</t>
+  </si>
+  <si>
+    <t>Gibraltar</t>
+  </si>
+  <si>
     <t>id_infraestructura</t>
   </si>
   <si>
@@ -967,7 +997,10 @@
     <t>nombre_batalla</t>
   </si>
   <si>
-    <t>fecha</t>
+    <t>fecha_inicio</t>
+  </si>
+  <si>
+    <t>fecha_fin</t>
   </si>
   <si>
     <t>Guerra</t>
@@ -1022,6 +1055,21 @@
   </si>
   <si>
     <t>victoria española</t>
+  </si>
+  <si>
+    <t>BAT00005</t>
+  </si>
+  <si>
+    <t>Bombardeo naval de Argel</t>
+  </si>
+  <si>
+    <t>01/08/1783</t>
+  </si>
+  <si>
+    <t>09/08/1783</t>
+  </si>
+  <si>
+    <t>Indepterminada.</t>
   </si>
   <si>
     <t>id_nacion</t>
@@ -1071,7 +1119,7 @@
     <numFmt numFmtId="167" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1120,6 +1168,11 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1149,7 +1202,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1171,12 +1224,18 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2083,11 +2142,64 @@
         <v>25.9889</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="8">
+        <v>35.2984</v>
+      </c>
+      <c r="D57" s="8">
+        <v>-2.935</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="8">
+        <v>36.1412</v>
+      </c>
+      <c r="D58" s="8">
+        <v>-5.4448</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="8">
+        <v>36.1381</v>
+      </c>
+      <c r="D59" s="8">
+        <v>-5.3538</v>
+      </c>
+    </row>
     <row r="60" ht="15.75" customHeight="1"/>
     <row r="61" ht="15.75" customHeight="1"/>
     <row r="62" ht="15.75" customHeight="1"/>
@@ -3051,19 +3163,19 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -3074,19 +3186,19 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F2" s="11">
         <v>36.495516</v>
@@ -3097,47 +3209,47 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
@@ -3145,13 +3257,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
@@ -3159,13 +3271,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
@@ -3179,13 +3291,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>44</v>
@@ -3193,13 +3305,13 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>42</v>
@@ -3207,104 +3319,104 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F15" s="11">
         <v>23.12653</v>
@@ -3315,36 +3427,36 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F17" s="11">
         <v>36.4942</v>
@@ -3355,70 +3467,70 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F21" s="8">
         <v>-12.0639</v>
@@ -3429,13 +3541,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>36</v>
@@ -3450,13 +3562,13 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
@@ -4458,417 +4570,417 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B38" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>256</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4893,98 +5005,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -5007,18 +5119,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5039,120 +5151,120 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -5169,128 +5281,155 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="29.63"/>
-    <col customWidth="1" min="4" max="4" width="28.88"/>
-    <col customWidth="1" min="5" max="5" width="13.25"/>
-    <col customWidth="1" min="6" max="6" width="13.38"/>
-    <col customWidth="1" min="7" max="7" width="21.75"/>
+    <col customWidth="1" min="4" max="4" width="9.63"/>
+    <col customWidth="1" min="5" max="5" width="28.88"/>
+    <col customWidth="1" min="6" max="6" width="13.25"/>
+    <col customWidth="1" min="7" max="7" width="13.38"/>
+    <col customWidth="1" min="8" max="8" width="21.75"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>325</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>316</v>
-      </c>
       <c r="H1" s="12" t="s">
-        <v>112</v>
+        <v>327</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E2" s="4">
+        <v>329</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="F2" s="4">
         <v>36.818056</v>
       </c>
-      <c r="F2" s="4">
+      <c r="G2" s="4">
         <v>-8.563611</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>321</v>
-      </c>
       <c r="H2" s="8" t="s">
-        <v>322</v>
+        <v>332</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="E3" s="7">
+        <v>335</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F3" s="7">
         <v>35.9257</v>
       </c>
-      <c r="F3" s="7">
+      <c r="G3" s="7">
         <v>-5.9109</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="E4" s="7">
+        <v>338</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="F4" s="7">
         <v>36.25</v>
       </c>
-      <c r="F4" s="7">
+      <c r="G4" s="7">
         <v>-6.2</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="E5" s="15">
-        <v>37.1718</v>
-      </c>
-      <c r="F5" s="15">
-        <v>4.5003</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>332</v>
+        <v>341</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="F5" s="16">
+        <v>36.1718</v>
+      </c>
+      <c r="G5" s="16">
+        <v>-4.5003</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>322</v>
+        <v>343</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="A6" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="F6" s="8">
+        <v>36.7651</v>
+      </c>
+      <c r="G6" s="8">
+        <v>3.1676</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="E7" s="7"/>
       <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -5312,50 +5451,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/LUGAR_CLAUDE.xlsx
+++ b/LUGAR_CLAUDE.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="363">
   <si>
     <t>id_lugar</t>
   </si>
@@ -1069,7 +1069,7 @@
     <t>09/08/1783</t>
   </si>
   <si>
-    <t>Indepterminada.</t>
+    <t>Indeterminada</t>
   </si>
   <si>
     <t>id_nacion</t>
@@ -1106,6 +1106,12 @@
   </si>
   <si>
     <t>Marruecos</t>
+  </si>
+  <si>
+    <t>NACI00006</t>
+  </si>
+  <si>
+    <t>Portugal</t>
   </si>
 </sst>
 </file>
@@ -5497,6 +5503,14 @@
         <v>360</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>362</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
